--- a/public/exports/29189781.xlsx
+++ b/public/exports/29189781.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089558</t>
+          <t xml:space="preserve">311089559</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089558</t>
+          <t xml:space="preserve">311089559</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089558</t>
+          <t xml:space="preserve">311089559</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">

--- a/public/exports/29189781.xlsx
+++ b/public/exports/29189781.xlsx
@@ -7864,7 +7864,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089558</t>
+          <t xml:space="preserve">311089560</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089558</t>
+          <t xml:space="preserve">311089560</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>

--- a/public/exports/29189781.xlsx
+++ b/public/exports/29189781.xlsx
@@ -7564,7 +7564,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089559</t>
+          <t xml:space="preserve">311089558</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089559</t>
+          <t xml:space="preserve">311089558</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089559</t>
+          <t xml:space="preserve">311089558</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089560</t>
+          <t xml:space="preserve">311089558</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089560</t>
+          <t xml:space="preserve">311089558</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
